--- a/Data/Analysis_Results.xlsx
+++ b/Data/Analysis_Results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ph. D\Paper\A topology-based approach for vulnerable pipe identification and modification in the urban drainage network\Publication\ASCE\R1\Figures\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Ph. D\Paper\A topology-based approach for vulnerable pipe identification and modification in the urban drainage network\Publication\ASCE\R1\Figures\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6B1C596-4355-4DD0-8393-1268B3511796}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F2B339D-B452-4D73-814A-C82F9934A91F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="4200" yWindow="4200" windowWidth="21600" windowHeight="11835" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Top_20_PVI" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="66" uniqueCount="17">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="14">
   <si>
     <t>Pipe</t>
   </si>
@@ -48,15 +48,6 @@
   </si>
   <si>
     <t>Downstream_Pipes</t>
-  </si>
-  <si>
-    <t>CPE1_Original</t>
-  </si>
-  <si>
-    <t>CPE2_Calculated</t>
-  </si>
-  <si>
-    <t>CPE_Weighted</t>
   </si>
   <si>
     <t>PVI</t>
@@ -471,22 +462,22 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1387,13 +1378,13 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -1683,10 +1674,10 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:P21"/>
+  <dimension ref="A1:N21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1712,31 +1703,25 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>338</v>
       </c>
@@ -1762,31 +1747,25 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>37.499999999999993</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="J2">
-        <v>1.2220201853215711</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="K2">
-        <v>11.43330302779823</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
-        <v>11.43330302779823</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>186</v>
       </c>
@@ -1812,31 +1791,25 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>24.789291026276651</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="J3">
-        <v>1.000000000000002</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="K3">
-        <v>7.5867873078829948</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>7.5867873078829948</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-      <c r="P3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>235</v>
       </c>
@@ -1862,31 +1835,25 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>24.21875</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="J4">
-        <v>1.0000000000000011</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="K4">
-        <v>7.4156249999999986</v>
+        <v>5.9</v>
       </c>
       <c r="L4">
-        <v>7.4156249999999986</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>36</v>
       </c>
@@ -1912,31 +1879,25 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>14.75774296902812</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="J5">
-        <v>6.8744059644345858</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="K5">
-        <v>5.4584837853736241</v>
+        <v>5.91</v>
       </c>
       <c r="L5">
-        <v>5.4584837853736241</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>5.91</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>4</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-      <c r="P5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -1962,31 +1923,25 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>14.75774296902812</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="J6">
-        <v>6.7713088794170346</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="K6">
-        <v>5.4430192226209906</v>
+        <v>5.91</v>
       </c>
       <c r="L6">
-        <v>5.4430192226209906</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5.91</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-      <c r="P6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>120</v>
       </c>
@@ -2012,31 +1967,25 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>11.990870786516849</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="J7">
-        <v>5.3565203725927004</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="K7">
-        <v>4.4007392918439612</v>
+        <v>5.89</v>
       </c>
       <c r="L7">
-        <v>4.4007392918439612</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
-      <c r="P7">
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>99</v>
       </c>
@@ -2062,31 +2011,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>9.5897435897435876</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="J8">
-        <v>6.4447717432626579</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="K8">
-        <v>3.8436388384124749</v>
+        <v>5.9</v>
       </c>
       <c r="L8">
-        <v>3.8436388384124749</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>7</v>
-      </c>
-      <c r="O8">
-        <v>7</v>
-      </c>
-      <c r="P8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>335</v>
       </c>
@@ -2112,31 +2055,25 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>12.5</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="J9">
-        <v>0.61084722178152673</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="K9">
-        <v>3.841627083267229</v>
+        <v>5.9</v>
       </c>
       <c r="L9">
-        <v>3.841627083267229</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>8</v>
-      </c>
-      <c r="O9">
-        <v>8</v>
-      </c>
-      <c r="P9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>154</v>
       </c>
@@ -2162,31 +2099,25 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>0.5116279069767441</v>
+        <v>3.006572989590159</v>
       </c>
       <c r="J10">
-        <v>19.02056411664757</v>
+        <v>2.9314086648504052</v>
       </c>
       <c r="K10">
-        <v>3.006572989590159</v>
+        <v>5.82</v>
       </c>
       <c r="L10">
-        <v>2.9314086648504052</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>5.82</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>9</v>
-      </c>
-      <c r="O10">
-        <v>9</v>
-      </c>
-      <c r="P10">
         <v>14</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>200</v>
       </c>
@@ -2212,31 +2143,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>9.07258064516129</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="J11">
-        <v>1.0827805840074221</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="K11">
-        <v>2.884191281149501</v>
+        <v>5.89</v>
       </c>
       <c r="L11">
-        <v>2.884191281149501</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>5.89</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>10</v>
-      </c>
-      <c r="O11">
-        <v>10</v>
-      </c>
-      <c r="P11">
         <v>9</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>208</v>
       </c>
@@ -2262,31 +2187,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>7.6990223463687144</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="J12">
-        <v>3.8144286104574179</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="K12">
-        <v>2.8818709954792272</v>
+        <v>5.87</v>
       </c>
       <c r="L12">
-        <v>2.8818709954792272</v>
+        <v>11</v>
       </c>
       <c r="M12">
-        <v>5.87</v>
+        <v>11</v>
       </c>
       <c r="N12">
-        <v>11</v>
-      </c>
-      <c r="O12">
-        <v>11</v>
-      </c>
-      <c r="P12">
         <v>11.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>174</v>
       </c>
@@ -2312,31 +2231,25 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>8.6975365765090373</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="J13">
-        <v>0.82604657324903374</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="K13">
-        <v>2.7331679589400659</v>
+        <v>5.84</v>
       </c>
       <c r="L13">
-        <v>2.7331679589400659</v>
+        <v>12</v>
       </c>
       <c r="M13">
-        <v>5.84</v>
+        <v>12</v>
       </c>
       <c r="N13">
-        <v>12</v>
-      </c>
-      <c r="O13">
-        <v>12</v>
-      </c>
-      <c r="P13">
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>303</v>
       </c>
@@ -2362,31 +2275,25 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0.51707848837209303</v>
+        <v>2.658868513427588</v>
       </c>
       <c r="J14">
-        <v>16.691633112773069</v>
+        <v>2.592396800591898</v>
       </c>
       <c r="K14">
-        <v>2.658868513427588</v>
+        <v>3.2</v>
       </c>
       <c r="L14">
-        <v>2.592396800591898</v>
+        <v>13</v>
       </c>
       <c r="M14">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="N14">
-        <v>13</v>
-      </c>
-      <c r="O14">
-        <v>14</v>
-      </c>
-      <c r="P14">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>314</v>
       </c>
@@ -2412,31 +2319,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0.65432000000000001</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="J15">
-        <v>15.56450511035775</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="K15">
-        <v>2.530971766553662</v>
+        <v>5.33</v>
       </c>
       <c r="L15">
-        <v>2.530971766553662</v>
+        <v>14</v>
       </c>
       <c r="M15">
-        <v>5.33</v>
+        <v>15</v>
       </c>
       <c r="N15">
-        <v>14</v>
-      </c>
-      <c r="O15">
-        <v>15</v>
-      </c>
-      <c r="P15">
         <v>16</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>319</v>
       </c>
@@ -2462,31 +2363,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0.2821538461538462</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="J16">
-        <v>16.160484665698611</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="K16">
-        <v>2.5087188537009459</v>
+        <v>5.08</v>
       </c>
       <c r="L16">
-        <v>2.5087188537009459</v>
+        <v>15</v>
       </c>
       <c r="M16">
-        <v>5.08</v>
+        <v>16</v>
       </c>
       <c r="N16">
-        <v>15</v>
-      </c>
-      <c r="O16">
-        <v>16</v>
-      </c>
-      <c r="P16">
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>125</v>
       </c>
@@ -2512,31 +2407,25 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>7.9471112388617424</v>
+        <v>2.498436732707856</v>
       </c>
       <c r="J17">
-        <v>0.76202240699555412</v>
+        <v>2.6233585693432491</v>
       </c>
       <c r="K17">
-        <v>2.498436732707856</v>
+        <v>5.87</v>
       </c>
       <c r="L17">
-        <v>2.6233585693432491</v>
+        <v>16</v>
       </c>
       <c r="M17">
-        <v>5.87</v>
+        <v>13</v>
       </c>
       <c r="N17">
-        <v>16</v>
-      </c>
-      <c r="O17">
-        <v>13</v>
-      </c>
-      <c r="P17">
         <v>11.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>311</v>
       </c>
@@ -2562,31 +2451,25 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.59799999999999998</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="J18">
-        <v>15.362973212868271</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="K18">
-        <v>2.4838459819302399</v>
+        <v>5.24</v>
       </c>
       <c r="L18">
-        <v>2.4838459819302399</v>
+        <v>17</v>
       </c>
       <c r="M18">
-        <v>5.24</v>
+        <v>18</v>
       </c>
       <c r="N18">
         <v>17</v>
       </c>
-      <c r="O18">
-        <v>18</v>
-      </c>
-      <c r="P18">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>98</v>
       </c>
@@ -2612,31 +2495,25 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>7.0379146919431266</v>
+        <v>2.3729600460436409</v>
       </c>
       <c r="J19">
-        <v>1.743904256404684</v>
+        <v>2.4916080483458232</v>
       </c>
       <c r="K19">
-        <v>2.3729600460436409</v>
+        <v>5.89</v>
       </c>
       <c r="L19">
-        <v>2.4916080483458232</v>
+        <v>18</v>
       </c>
       <c r="M19">
-        <v>5.89</v>
+        <v>17</v>
       </c>
       <c r="N19">
-        <v>18</v>
-      </c>
-      <c r="O19">
-        <v>17</v>
-      </c>
-      <c r="P19">
         <v>9</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>132</v>
       </c>
@@ -2662,31 +2539,25 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.37031209021767642</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="J20">
-        <v>15.03840379543699</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="K20">
-        <v>2.366854196380852</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="L20">
-        <v>2.366854196380852</v>
+        <v>19</v>
       </c>
       <c r="M20">
-        <v>4.6900000000000004</v>
+        <v>20</v>
       </c>
       <c r="N20">
         <v>19</v>
       </c>
-      <c r="O20">
-        <v>20</v>
-      </c>
-      <c r="P20">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>309</v>
       </c>
@@ -2712,27 +2583,21 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5260162601626015</v>
+        <v>2.3129806668929591</v>
       </c>
       <c r="J21">
-        <v>14.36783859229452</v>
+        <v>2.4286297002376069</v>
       </c>
       <c r="K21">
-        <v>2.3129806668929591</v>
+        <v>5.42</v>
       </c>
       <c r="L21">
-        <v>2.4286297002376069</v>
+        <v>20</v>
       </c>
       <c r="M21">
-        <v>5.42</v>
+        <v>19</v>
       </c>
       <c r="N21">
-        <v>20</v>
-      </c>
-      <c r="O21">
-        <v>19</v>
-      </c>
-      <c r="P21">
         <v>15</v>
       </c>
     </row>
@@ -2743,10 +2608,10 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2772,31 +2637,25 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>338</v>
       </c>
@@ -2822,31 +2681,25 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>37.499999999999993</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="J2">
-        <v>1.2220201853215711</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="K2">
-        <v>11.43330302779823</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
-        <v>11.43330302779823</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>186</v>
       </c>
@@ -2872,31 +2725,25 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>24.789291026276651</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="J3">
-        <v>1.000000000000002</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="K3">
-        <v>7.5867873078829948</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>7.5867873078829948</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-      <c r="P3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>235</v>
       </c>
@@ -2922,31 +2769,25 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>24.21875</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="J4">
-        <v>1.0000000000000011</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="K4">
-        <v>7.4156249999999986</v>
+        <v>5.9</v>
       </c>
       <c r="L4">
-        <v>7.4156249999999986</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>36</v>
       </c>
@@ -2972,31 +2813,25 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>14.75774296902812</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="J5">
-        <v>6.8744059644345858</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="K5">
-        <v>5.4584837853736241</v>
+        <v>5.91</v>
       </c>
       <c r="L5">
-        <v>5.4584837853736241</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>5.91</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>4</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-      <c r="P5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -3022,31 +2857,25 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>14.75774296902812</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="J6">
-        <v>6.7713088794170346</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="K6">
-        <v>5.4430192226209906</v>
+        <v>5.91</v>
       </c>
       <c r="L6">
-        <v>5.4430192226209906</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5.91</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-      <c r="P6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>120</v>
       </c>
@@ -3072,31 +2901,25 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>11.990870786516849</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="J7">
-        <v>5.3565203725927004</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="K7">
-        <v>4.4007392918439612</v>
+        <v>5.89</v>
       </c>
       <c r="L7">
-        <v>4.4007392918439612</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
-      <c r="P7">
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>99</v>
       </c>
@@ -3122,31 +2945,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>9.5897435897435876</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="J8">
-        <v>6.4447717432626579</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="K8">
-        <v>3.8436388384124749</v>
+        <v>5.9</v>
       </c>
       <c r="L8">
-        <v>3.8436388384124749</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>7</v>
-      </c>
-      <c r="O8">
-        <v>7</v>
-      </c>
-      <c r="P8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>335</v>
       </c>
@@ -3172,31 +2989,25 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>12.5</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="J9">
-        <v>0.61084722178152673</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="K9">
-        <v>3.841627083267229</v>
+        <v>5.9</v>
       </c>
       <c r="L9">
-        <v>3.841627083267229</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>8</v>
-      </c>
-      <c r="O9">
-        <v>8</v>
-      </c>
-      <c r="P9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>154</v>
       </c>
@@ -3222,31 +3033,25 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>0.5116279069767441</v>
+        <v>3.006572989590159</v>
       </c>
       <c r="J10">
-        <v>19.02056411664757</v>
+        <v>2.9314086648504052</v>
       </c>
       <c r="K10">
-        <v>3.006572989590159</v>
+        <v>5.82</v>
       </c>
       <c r="L10">
-        <v>2.9314086648504052</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>5.82</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>9</v>
-      </c>
-      <c r="O10">
-        <v>9</v>
-      </c>
-      <c r="P10">
         <v>17</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>200</v>
       </c>
@@ -3272,31 +3077,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>9.07258064516129</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="J11">
-        <v>1.0827805840074221</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="K11">
-        <v>2.884191281149501</v>
+        <v>5.89</v>
       </c>
       <c r="L11">
-        <v>2.884191281149501</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>5.89</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>10</v>
-      </c>
-      <c r="O11">
-        <v>10</v>
-      </c>
-      <c r="P11">
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>208</v>
       </c>
@@ -3322,31 +3121,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>7.6990223463687144</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="J12">
-        <v>3.8144286104574179</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="K12">
-        <v>2.8818709954792272</v>
+        <v>5.87</v>
       </c>
       <c r="L12">
-        <v>2.8818709954792272</v>
+        <v>11</v>
       </c>
       <c r="M12">
-        <v>5.87</v>
+        <v>11</v>
       </c>
       <c r="N12">
-        <v>11</v>
-      </c>
-      <c r="O12">
-        <v>11</v>
-      </c>
-      <c r="P12">
         <v>12.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>174</v>
       </c>
@@ -3372,31 +3165,25 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>8.6975365765090373</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="J13">
-        <v>0.82604657324903374</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="K13">
-        <v>2.7331679589400659</v>
+        <v>5.84</v>
       </c>
       <c r="L13">
-        <v>2.7331679589400659</v>
+        <v>12</v>
       </c>
       <c r="M13">
-        <v>5.84</v>
+        <v>12</v>
       </c>
       <c r="N13">
-        <v>12</v>
-      </c>
-      <c r="O13">
-        <v>12</v>
-      </c>
-      <c r="P13">
         <v>15.5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>125</v>
       </c>
@@ -3422,31 +3209,25 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>7.9471112388617424</v>
+        <v>2.498436732707856</v>
       </c>
       <c r="J14">
-        <v>0.76202240699555412</v>
+        <v>2.6233585693432491</v>
       </c>
       <c r="K14">
-        <v>2.498436732707856</v>
+        <v>5.87</v>
       </c>
       <c r="L14">
-        <v>2.6233585693432491</v>
+        <v>16</v>
       </c>
       <c r="M14">
-        <v>5.87</v>
+        <v>13</v>
       </c>
       <c r="N14">
-        <v>16</v>
-      </c>
-      <c r="O14">
-        <v>13</v>
-      </c>
-      <c r="P14">
         <v>12.5</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>303</v>
       </c>
@@ -3472,31 +3253,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0.51707848837209303</v>
+        <v>2.658868513427588</v>
       </c>
       <c r="J15">
-        <v>16.691633112773069</v>
+        <v>2.592396800591898</v>
       </c>
       <c r="K15">
-        <v>2.658868513427588</v>
+        <v>3.2</v>
       </c>
       <c r="L15">
-        <v>2.592396800591898</v>
+        <v>13</v>
       </c>
       <c r="M15">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="N15">
-        <v>13</v>
-      </c>
-      <c r="O15">
-        <v>14</v>
-      </c>
-      <c r="P15">
         <v>29</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>314</v>
       </c>
@@ -3522,31 +3297,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0.65432000000000001</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="J16">
-        <v>15.56450511035775</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="K16">
-        <v>2.530971766553662</v>
+        <v>5.33</v>
       </c>
       <c r="L16">
-        <v>2.530971766553662</v>
+        <v>14</v>
       </c>
       <c r="M16">
-        <v>5.33</v>
+        <v>15</v>
       </c>
       <c r="N16">
-        <v>14</v>
-      </c>
-      <c r="O16">
-        <v>15</v>
-      </c>
-      <c r="P16">
         <v>20.5</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>150</v>
       </c>
@@ -3572,31 +3341,25 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>4.8</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="J17">
-        <v>5.6938500468224236</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="K17">
-        <v>2.5087188537009459</v>
+        <v>5.08</v>
       </c>
       <c r="L17">
-        <v>2.5087188537009459</v>
+        <v>15</v>
       </c>
       <c r="M17">
-        <v>5.08</v>
+        <v>16</v>
       </c>
       <c r="N17">
-        <v>15</v>
-      </c>
-      <c r="O17">
-        <v>16</v>
-      </c>
-      <c r="P17">
         <v>24</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>319</v>
       </c>
@@ -3622,31 +3385,25 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.2821538461538462</v>
+        <v>2.3729600460436409</v>
       </c>
       <c r="J18">
-        <v>16.160484665698611</v>
+        <v>2.4916080483458232</v>
       </c>
       <c r="K18">
-        <v>2.3729600460436409</v>
+        <v>5.89</v>
       </c>
       <c r="L18">
-        <v>2.4916080483458232</v>
+        <v>18</v>
       </c>
       <c r="M18">
-        <v>5.89</v>
+        <v>17</v>
       </c>
       <c r="N18">
-        <v>18</v>
-      </c>
-      <c r="O18">
-        <v>17</v>
-      </c>
-      <c r="P18">
         <v>9.5</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>98</v>
       </c>
@@ -3672,31 +3429,25 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>7.0379146919431266</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="J19">
-        <v>1.743904256404684</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="K19">
-        <v>2.4838459819302399</v>
+        <v>5.24</v>
       </c>
       <c r="L19">
-        <v>2.4838459819302399</v>
+        <v>17</v>
       </c>
       <c r="M19">
-        <v>5.24</v>
+        <v>18</v>
       </c>
       <c r="N19">
-        <v>17</v>
-      </c>
-      <c r="O19">
-        <v>18</v>
-      </c>
-      <c r="P19">
         <v>22</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>311</v>
       </c>
@@ -3722,31 +3473,25 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.59799999999999998</v>
+        <v>2.3129806668929591</v>
       </c>
       <c r="J20">
-        <v>15.362973212868271</v>
+        <v>2.4286297002376069</v>
       </c>
       <c r="K20">
-        <v>2.3129806668929591</v>
+        <v>5.42</v>
       </c>
       <c r="L20">
-        <v>2.4286297002376069</v>
+        <v>21.5</v>
       </c>
       <c r="M20">
-        <v>5.42</v>
+        <v>19.5</v>
       </c>
       <c r="N20">
-        <v>21.5</v>
-      </c>
-      <c r="O20">
-        <v>19.5</v>
-      </c>
-      <c r="P20">
         <v>18.5</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>136</v>
       </c>
@@ -3772,31 +3517,25 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.78865882352941186</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="J21">
-        <v>13.30070280964677</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="K21">
-        <v>2.366854196380852</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="L21">
-        <v>2.366854196380852</v>
+        <v>19.5</v>
       </c>
       <c r="M21">
-        <v>4.6900000000000004</v>
+        <v>22.5</v>
       </c>
       <c r="N21">
-        <v>19.5</v>
-      </c>
-      <c r="O21">
-        <v>22.5</v>
-      </c>
-      <c r="P21">
         <v>26.5</v>
       </c>
     </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>309</v>
       </c>
@@ -3822,31 +3561,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>0.5260162601626015</v>
+        <v>2.3129806668929591</v>
       </c>
       <c r="J22">
-        <v>14.36783859229452</v>
+        <v>2.4286297002376069</v>
       </c>
       <c r="K22">
-        <v>2.3129806668929591</v>
+        <v>5.42</v>
       </c>
       <c r="L22">
-        <v>2.4286297002376069</v>
+        <v>21.5</v>
       </c>
       <c r="M22">
-        <v>5.42</v>
+        <v>19.5</v>
       </c>
       <c r="N22">
-        <v>21.5</v>
-      </c>
-      <c r="O22">
-        <v>19.5</v>
-      </c>
-      <c r="P22">
         <v>18.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>100</v>
       </c>
@@ -3872,31 +3605,25 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>2.9730496453900721</v>
+        <v>2.1741524456571848</v>
       </c>
       <c r="J23">
-        <v>8.548250346934422</v>
+        <v>2.37852277554896</v>
       </c>
       <c r="K23">
-        <v>2.1741524456571848</v>
+        <v>5.86</v>
       </c>
       <c r="L23">
-        <v>2.37852277554896</v>
+        <v>23</v>
       </c>
       <c r="M23">
-        <v>5.86</v>
+        <v>21</v>
       </c>
       <c r="N23">
-        <v>23</v>
-      </c>
-      <c r="O23">
-        <v>21</v>
-      </c>
-      <c r="P23">
         <v>14</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>132</v>
       </c>
@@ -3922,31 +3649,25 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>0.37031209021767642</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="J24">
-        <v>15.03840379543699</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="K24">
-        <v>2.366854196380852</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="L24">
-        <v>2.366854196380852</v>
+        <v>19.5</v>
       </c>
       <c r="M24">
-        <v>4.6900000000000004</v>
+        <v>22.5</v>
       </c>
       <c r="N24">
-        <v>19.5</v>
-      </c>
-      <c r="O24">
-        <v>22.5</v>
-      </c>
-      <c r="P24">
         <v>26.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>172</v>
       </c>
@@ -3972,31 +3693,25 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4.4142454326828764</v>
+        <v>2.1470877075261372</v>
       </c>
       <c r="J25">
-        <v>5.485427184808497</v>
+        <v>2.3489139520335942</v>
       </c>
       <c r="K25">
-        <v>2.1470877075261372</v>
+        <v>5.84</v>
       </c>
       <c r="L25">
-        <v>2.3489139520335942</v>
+        <v>24</v>
       </c>
       <c r="M25">
-        <v>5.84</v>
+        <v>24</v>
       </c>
       <c r="N25">
-        <v>24</v>
-      </c>
-      <c r="O25">
-        <v>24</v>
-      </c>
-      <c r="P25">
         <v>15.5</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>297</v>
       </c>
@@ -4022,31 +3737,25 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>5.9390243902439028</v>
+        <v>1.962802177102003</v>
       </c>
       <c r="J26">
-        <v>1.207299066858883</v>
+        <v>2.147305581749591</v>
       </c>
       <c r="K26">
-        <v>1.962802177102003</v>
+        <v>5.89</v>
       </c>
       <c r="L26">
-        <v>2.147305581749591</v>
+        <v>25</v>
       </c>
       <c r="M26">
-        <v>5.89</v>
+        <v>25</v>
       </c>
       <c r="N26">
-        <v>25</v>
-      </c>
-      <c r="O26">
-        <v>25</v>
-      </c>
-      <c r="P26">
         <v>9.5</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>156</v>
       </c>
@@ -4072,31 +3781,25 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0.33108494983277598</v>
+        <v>1.9442259245037321</v>
       </c>
       <c r="J27">
-        <v>12.299336263692661</v>
+        <v>2.1269831614070829</v>
       </c>
       <c r="K27">
-        <v>1.9442259245037321</v>
+        <v>5.33</v>
       </c>
       <c r="L27">
-        <v>2.1269831614070829</v>
+        <v>26</v>
       </c>
       <c r="M27">
-        <v>5.33</v>
+        <v>26</v>
       </c>
       <c r="N27">
-        <v>26</v>
-      </c>
-      <c r="O27">
-        <v>26</v>
-      </c>
-      <c r="P27">
         <v>20.5</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>112</v>
       </c>
@@ -4122,31 +3825,25 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>0.99935515361505822</v>
+        <v>1.8933596063359861</v>
       </c>
       <c r="J28">
-        <v>10.623687068343131</v>
+        <v>2.071335409331569</v>
       </c>
       <c r="K28">
-        <v>1.8933596063359861</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="L28">
-        <v>2.071335409331569</v>
+        <v>27</v>
       </c>
       <c r="M28">
-        <v>5.1100000000000003</v>
+        <v>27</v>
       </c>
       <c r="N28">
-        <v>27</v>
-      </c>
-      <c r="O28">
-        <v>27</v>
-      </c>
-      <c r="P28">
         <v>23</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>39</v>
       </c>
@@ -4172,31 +3869,25 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1.9261181640625</v>
+        <v>1.8879382948400121</v>
       </c>
       <c r="J29">
-        <v>8.7340189708084122</v>
+        <v>2.065404494554973</v>
       </c>
       <c r="K29">
-        <v>1.8879382948400121</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="L29">
-        <v>2.065404494554973</v>
+        <v>28</v>
       </c>
       <c r="M29">
-        <v>4.1900000000000004</v>
+        <v>28</v>
       </c>
       <c r="N29">
         <v>28</v>
       </c>
-      <c r="O29">
-        <v>28</v>
-      </c>
-      <c r="P29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>45</v>
       </c>
@@ -4222,31 +3913,25 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0.46783088235294118</v>
+        <v>1.875862643515253</v>
       </c>
       <c r="J30">
-        <v>11.57008919206247</v>
+        <v>2.0521937320056871</v>
       </c>
       <c r="K30">
-        <v>1.875862643515253</v>
+        <v>0.96</v>
       </c>
       <c r="L30">
-        <v>2.0521937320056871</v>
+        <v>29</v>
       </c>
       <c r="M30">
-        <v>0.96</v>
+        <v>29</v>
       </c>
       <c r="N30">
-        <v>29</v>
-      </c>
-      <c r="O30">
-        <v>29</v>
-      </c>
-      <c r="P30">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>203</v>
       </c>
@@ -4272,27 +3957,21 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0.64117187499999995</v>
+        <v>1.8674013406850849</v>
       </c>
       <c r="J31">
-        <v>11.1669985212339</v>
+        <v>2.0429370667094831</v>
       </c>
       <c r="K31">
-        <v>1.8674013406850849</v>
+        <v>4.92</v>
       </c>
       <c r="L31">
-        <v>2.0429370667094831</v>
+        <v>30</v>
       </c>
       <c r="M31">
-        <v>4.92</v>
+        <v>30</v>
       </c>
       <c r="N31">
-        <v>30</v>
-      </c>
-      <c r="O31">
-        <v>30</v>
-      </c>
-      <c r="P31">
         <v>25</v>
       </c>
     </row>
@@ -4303,10 +3982,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4332,31 +4011,25 @@
         <v>7</v>
       </c>
       <c r="I1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="J1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="1" t="s">
+      <c r="K1" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="L1" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="L1" s="1" t="s">
+      <c r="M1" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
+      <c r="N1" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="N1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" s="1" t="s">
-        <v>14</v>
-      </c>
-      <c r="P1" s="1" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>338</v>
       </c>
@@ -4382,31 +4055,25 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>37.499999999999993</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="J2">
-        <v>1.2220201853215711</v>
+        <v>11.43330302779823</v>
       </c>
       <c r="K2">
-        <v>11.43330302779823</v>
+        <v>5.9</v>
       </c>
       <c r="L2">
-        <v>11.43330302779823</v>
+        <v>1</v>
       </c>
       <c r="M2">
-        <v>5.9</v>
+        <v>1</v>
       </c>
       <c r="N2">
-        <v>1</v>
-      </c>
-      <c r="O2">
-        <v>1</v>
-      </c>
-      <c r="P2">
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>186</v>
       </c>
@@ -4432,31 +4099,25 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>24.789291026276651</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="J3">
-        <v>1.000000000000002</v>
+        <v>7.5867873078829948</v>
       </c>
       <c r="K3">
-        <v>7.5867873078829948</v>
+        <v>5.9</v>
       </c>
       <c r="L3">
-        <v>7.5867873078829948</v>
+        <v>2</v>
       </c>
       <c r="M3">
-        <v>5.9</v>
+        <v>2</v>
       </c>
       <c r="N3">
-        <v>2</v>
-      </c>
-      <c r="O3">
-        <v>2</v>
-      </c>
-      <c r="P3">
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>235</v>
       </c>
@@ -4482,31 +4143,25 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>24.21875</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="J4">
-        <v>1.0000000000000011</v>
+        <v>7.4156249999999986</v>
       </c>
       <c r="K4">
-        <v>7.4156249999999986</v>
+        <v>5.9</v>
       </c>
       <c r="L4">
-        <v>7.4156249999999986</v>
+        <v>3</v>
       </c>
       <c r="M4">
-        <v>5.9</v>
+        <v>3</v>
       </c>
       <c r="N4">
-        <v>3</v>
-      </c>
-      <c r="O4">
-        <v>3</v>
-      </c>
-      <c r="P4">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>36</v>
       </c>
@@ -4532,31 +4187,25 @@
         <v>1</v>
       </c>
       <c r="I5">
-        <v>14.75774296902812</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="J5">
-        <v>6.8744059644345858</v>
+        <v>5.4584837853736241</v>
       </c>
       <c r="K5">
-        <v>5.4584837853736241</v>
+        <v>5.91</v>
       </c>
       <c r="L5">
-        <v>5.4584837853736241</v>
+        <v>4</v>
       </c>
       <c r="M5">
-        <v>5.91</v>
+        <v>4</v>
       </c>
       <c r="N5">
-        <v>4</v>
-      </c>
-      <c r="O5">
-        <v>4</v>
-      </c>
-      <c r="P5">
         <v>1.5</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>34</v>
       </c>
@@ -4582,31 +4231,25 @@
         <v>1</v>
       </c>
       <c r="I6">
-        <v>14.75774296902812</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="J6">
-        <v>6.7713088794170346</v>
+        <v>5.4430192226209906</v>
       </c>
       <c r="K6">
-        <v>5.4430192226209906</v>
+        <v>5.91</v>
       </c>
       <c r="L6">
-        <v>5.4430192226209906</v>
+        <v>5</v>
       </c>
       <c r="M6">
-        <v>5.91</v>
+        <v>5</v>
       </c>
       <c r="N6">
-        <v>5</v>
-      </c>
-      <c r="O6">
-        <v>5</v>
-      </c>
-      <c r="P6">
         <v>1.5</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>120</v>
       </c>
@@ -4632,31 +4275,25 @@
         <v>1</v>
       </c>
       <c r="I7">
-        <v>11.990870786516849</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="J7">
-        <v>5.3565203725927004</v>
+        <v>4.4007392918439612</v>
       </c>
       <c r="K7">
-        <v>4.4007392918439612</v>
+        <v>5.89</v>
       </c>
       <c r="L7">
-        <v>4.4007392918439612</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>5.89</v>
+        <v>6</v>
       </c>
       <c r="N7">
-        <v>6</v>
-      </c>
-      <c r="O7">
-        <v>6</v>
-      </c>
-      <c r="P7">
         <v>9.5</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>99</v>
       </c>
@@ -4682,31 +4319,25 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>9.5897435897435876</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="J8">
-        <v>6.4447717432626579</v>
+        <v>3.8436388384124749</v>
       </c>
       <c r="K8">
-        <v>3.8436388384124749</v>
+        <v>5.9</v>
       </c>
       <c r="L8">
-        <v>3.8436388384124749</v>
+        <v>7</v>
       </c>
       <c r="M8">
-        <v>5.9</v>
+        <v>7</v>
       </c>
       <c r="N8">
-        <v>7</v>
-      </c>
-      <c r="O8">
-        <v>7</v>
-      </c>
-      <c r="P8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>335</v>
       </c>
@@ -4732,31 +4363,25 @@
         <v>1</v>
       </c>
       <c r="I9">
-        <v>12.5</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="J9">
-        <v>0.61084722178152673</v>
+        <v>3.841627083267229</v>
       </c>
       <c r="K9">
-        <v>3.841627083267229</v>
+        <v>5.9</v>
       </c>
       <c r="L9">
-        <v>3.841627083267229</v>
+        <v>8</v>
       </c>
       <c r="M9">
-        <v>5.9</v>
+        <v>8</v>
       </c>
       <c r="N9">
-        <v>8</v>
-      </c>
-      <c r="O9">
-        <v>8</v>
-      </c>
-      <c r="P9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>154</v>
       </c>
@@ -4782,31 +4407,25 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>0.5116279069767441</v>
+        <v>3.006572989590159</v>
       </c>
       <c r="J10">
-        <v>19.02056411664757</v>
+        <v>2.9314086648504052</v>
       </c>
       <c r="K10">
-        <v>3.006572989590159</v>
+        <v>5.82</v>
       </c>
       <c r="L10">
-        <v>2.9314086648504052</v>
+        <v>9</v>
       </c>
       <c r="M10">
-        <v>5.82</v>
+        <v>9</v>
       </c>
       <c r="N10">
-        <v>9</v>
-      </c>
-      <c r="O10">
-        <v>9</v>
-      </c>
-      <c r="P10">
         <v>18</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>200</v>
       </c>
@@ -4832,31 +4451,25 @@
         <v>1</v>
       </c>
       <c r="I11">
-        <v>9.07258064516129</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="J11">
-        <v>1.0827805840074221</v>
+        <v>2.884191281149501</v>
       </c>
       <c r="K11">
-        <v>2.884191281149501</v>
+        <v>5.89</v>
       </c>
       <c r="L11">
-        <v>2.884191281149501</v>
+        <v>10</v>
       </c>
       <c r="M11">
-        <v>5.89</v>
+        <v>10</v>
       </c>
       <c r="N11">
-        <v>10</v>
-      </c>
-      <c r="O11">
-        <v>10</v>
-      </c>
-      <c r="P11">
         <v>9.5</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>208</v>
       </c>
@@ -4882,31 +4495,25 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>7.6990223463687144</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="J12">
-        <v>3.8144286104574179</v>
+        <v>2.8818709954792272</v>
       </c>
       <c r="K12">
-        <v>2.8818709954792272</v>
+        <v>5.87</v>
       </c>
       <c r="L12">
-        <v>2.8818709954792272</v>
+        <v>11</v>
       </c>
       <c r="M12">
-        <v>5.87</v>
+        <v>11</v>
       </c>
       <c r="N12">
-        <v>11</v>
-      </c>
-      <c r="O12">
-        <v>11</v>
-      </c>
-      <c r="P12">
         <v>12.5</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13">
         <v>174</v>
       </c>
@@ -4932,31 +4539,25 @@
         <v>1</v>
       </c>
       <c r="I13">
-        <v>8.6975365765090373</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="J13">
-        <v>0.82604657324903374</v>
+        <v>2.7331679589400659</v>
       </c>
       <c r="K13">
-        <v>2.7331679589400659</v>
+        <v>5.84</v>
       </c>
       <c r="L13">
-        <v>2.7331679589400659</v>
+        <v>12</v>
       </c>
       <c r="M13">
-        <v>5.84</v>
+        <v>12</v>
       </c>
       <c r="N13">
-        <v>12</v>
-      </c>
-      <c r="O13">
-        <v>12</v>
-      </c>
-      <c r="P13">
         <v>16.5</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A14">
         <v>303</v>
       </c>
@@ -4982,31 +4583,25 @@
         <v>1</v>
       </c>
       <c r="I14">
-        <v>0.51707848837209303</v>
+        <v>2.658868513427588</v>
       </c>
       <c r="J14">
-        <v>16.691633112773069</v>
+        <v>2.592396800591898</v>
       </c>
       <c r="K14">
-        <v>2.658868513427588</v>
+        <v>3.2</v>
       </c>
       <c r="L14">
-        <v>2.592396800591898</v>
+        <v>13</v>
       </c>
       <c r="M14">
-        <v>3.2</v>
+        <v>14</v>
       </c>
       <c r="N14">
-        <v>13</v>
-      </c>
-      <c r="O14">
-        <v>14</v>
-      </c>
-      <c r="P14">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A15">
         <v>314</v>
       </c>
@@ -5032,31 +4627,25 @@
         <v>1</v>
       </c>
       <c r="I15">
-        <v>0.65432000000000001</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="J15">
-        <v>15.56450511035775</v>
+        <v>2.530971766553662</v>
       </c>
       <c r="K15">
-        <v>2.530971766553662</v>
+        <v>5.33</v>
       </c>
       <c r="L15">
-        <v>2.530971766553662</v>
+        <v>14</v>
       </c>
       <c r="M15">
-        <v>5.33</v>
+        <v>15</v>
       </c>
       <c r="N15">
-        <v>14</v>
-      </c>
-      <c r="O15">
-        <v>15</v>
-      </c>
-      <c r="P15">
         <v>21.5</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A16">
         <v>319</v>
       </c>
@@ -5082,31 +4671,25 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>0.2821538461538462</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="J16">
-        <v>16.160484665698611</v>
+        <v>2.5087188537009459</v>
       </c>
       <c r="K16">
-        <v>2.5087188537009459</v>
+        <v>5.08</v>
       </c>
       <c r="L16">
-        <v>2.5087188537009459</v>
+        <v>15</v>
       </c>
       <c r="M16">
-        <v>5.08</v>
+        <v>16</v>
       </c>
       <c r="N16">
-        <v>15</v>
-      </c>
-      <c r="O16">
-        <v>16</v>
-      </c>
-      <c r="P16">
         <v>25</v>
       </c>
     </row>
-    <row r="17" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A17">
         <v>125</v>
       </c>
@@ -5132,31 +4715,25 @@
         <v>1</v>
       </c>
       <c r="I17">
-        <v>7.9471112388617424</v>
+        <v>2.498436732707856</v>
       </c>
       <c r="J17">
-        <v>0.76202240699555412</v>
+        <v>2.6233585693432491</v>
       </c>
       <c r="K17">
-        <v>2.498436732707856</v>
+        <v>5.87</v>
       </c>
       <c r="L17">
-        <v>2.6233585693432491</v>
+        <v>16</v>
       </c>
       <c r="M17">
-        <v>5.87</v>
+        <v>13</v>
       </c>
       <c r="N17">
-        <v>16</v>
-      </c>
-      <c r="O17">
-        <v>13</v>
-      </c>
-      <c r="P17">
         <v>12.5</v>
       </c>
     </row>
-    <row r="18" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A18">
         <v>311</v>
       </c>
@@ -5182,31 +4759,25 @@
         <v>1</v>
       </c>
       <c r="I18">
-        <v>0.59799999999999998</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="J18">
-        <v>15.362973212868271</v>
+        <v>2.4838459819302399</v>
       </c>
       <c r="K18">
-        <v>2.4838459819302399</v>
+        <v>5.24</v>
       </c>
       <c r="L18">
-        <v>2.4838459819302399</v>
+        <v>17</v>
       </c>
       <c r="M18">
-        <v>5.24</v>
+        <v>18</v>
       </c>
       <c r="N18">
-        <v>17</v>
-      </c>
-      <c r="O18">
-        <v>18</v>
-      </c>
-      <c r="P18">
         <v>23</v>
       </c>
     </row>
-    <row r="19" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A19">
         <v>98</v>
       </c>
@@ -5232,31 +4803,25 @@
         <v>1</v>
       </c>
       <c r="I19">
-        <v>7.0379146919431266</v>
+        <v>2.3729600460436409</v>
       </c>
       <c r="J19">
-        <v>1.743904256404684</v>
+        <v>2.4916080483458232</v>
       </c>
       <c r="K19">
-        <v>2.3729600460436409</v>
+        <v>5.89</v>
       </c>
       <c r="L19">
-        <v>2.4916080483458232</v>
+        <v>18</v>
       </c>
       <c r="M19">
-        <v>5.89</v>
+        <v>17</v>
       </c>
       <c r="N19">
-        <v>18</v>
-      </c>
-      <c r="O19">
-        <v>17</v>
-      </c>
-      <c r="P19">
         <v>9.5</v>
       </c>
     </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A20">
         <v>132</v>
       </c>
@@ -5282,31 +4847,25 @@
         <v>1</v>
       </c>
       <c r="I20">
-        <v>0.37031209021767642</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="J20">
-        <v>15.03840379543699</v>
+        <v>2.366854196380852</v>
       </c>
       <c r="K20">
-        <v>2.366854196380852</v>
+        <v>4.6900000000000004</v>
       </c>
       <c r="L20">
-        <v>2.366854196380852</v>
+        <v>19</v>
       </c>
       <c r="M20">
-        <v>4.6900000000000004</v>
+        <v>20</v>
       </c>
       <c r="N20">
-        <v>19</v>
-      </c>
-      <c r="O20">
-        <v>20</v>
-      </c>
-      <c r="P20">
         <v>27</v>
       </c>
     </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A21">
         <v>309</v>
       </c>
@@ -5332,31 +4891,25 @@
         <v>1</v>
       </c>
       <c r="I21">
-        <v>0.5260162601626015</v>
+        <v>2.3129806668929591</v>
       </c>
       <c r="J21">
-        <v>14.36783859229452</v>
+        <v>2.4286297002376069</v>
       </c>
       <c r="K21">
-        <v>2.3129806668929591</v>
+        <v>5.42</v>
       </c>
       <c r="L21">
-        <v>2.4286297002376069</v>
+        <v>20</v>
       </c>
       <c r="M21">
-        <v>5.42</v>
+        <v>19</v>
       </c>
       <c r="N21">
         <v>20</v>
       </c>
-      <c r="O21">
-        <v>19</v>
-      </c>
-      <c r="P21">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A22">
         <v>150</v>
       </c>
@@ -5382,31 +4935,25 @@
         <v>1</v>
       </c>
       <c r="I22">
-        <v>4.8</v>
+        <v>2.294077507023363</v>
       </c>
       <c r="J22">
-        <v>5.6938500468224236</v>
+        <v>2.294077507023363</v>
       </c>
       <c r="K22">
-        <v>2.294077507023363</v>
+        <v>5.86</v>
       </c>
       <c r="L22">
-        <v>2.294077507023363</v>
+        <v>21</v>
       </c>
       <c r="M22">
-        <v>5.86</v>
+        <v>21</v>
       </c>
       <c r="N22">
-        <v>21</v>
-      </c>
-      <c r="O22">
-        <v>21</v>
-      </c>
-      <c r="P22">
         <v>14.5</v>
       </c>
     </row>
-    <row r="23" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A23">
         <v>136</v>
       </c>
@@ -5432,31 +4979,25 @@
         <v>1</v>
       </c>
       <c r="I23">
-        <v>0.78865882352941186</v>
+        <v>2.2317030685058392</v>
       </c>
       <c r="J23">
-        <v>13.30070280964677</v>
+        <v>2.2317030685058392</v>
       </c>
       <c r="K23">
-        <v>2.2317030685058392</v>
+        <v>5.78</v>
       </c>
       <c r="L23">
-        <v>2.2317030685058392</v>
+        <v>22</v>
       </c>
       <c r="M23">
-        <v>5.78</v>
+        <v>22</v>
       </c>
       <c r="N23">
-        <v>22</v>
-      </c>
-      <c r="O23">
-        <v>22</v>
-      </c>
-      <c r="P23">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A24">
         <v>100</v>
       </c>
@@ -5482,31 +5023,25 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>2.9730496453900721</v>
+        <v>2.1741524456571848</v>
       </c>
       <c r="J24">
-        <v>8.548250346934422</v>
+        <v>2.1741524456571848</v>
       </c>
       <c r="K24">
-        <v>2.1741524456571848</v>
+        <v>5.86</v>
       </c>
       <c r="L24">
-        <v>2.1741524456571848</v>
+        <v>23</v>
       </c>
       <c r="M24">
-        <v>5.86</v>
+        <v>23</v>
       </c>
       <c r="N24">
-        <v>23</v>
-      </c>
-      <c r="O24">
-        <v>23</v>
-      </c>
-      <c r="P24">
         <v>14.5</v>
       </c>
     </row>
-    <row r="25" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A25">
         <v>172</v>
       </c>
@@ -5532,31 +5067,25 @@
         <v>1</v>
       </c>
       <c r="I25">
-        <v>4.4142454326828764</v>
+        <v>2.1470877075261372</v>
       </c>
       <c r="J25">
-        <v>5.485427184808497</v>
+        <v>2.1470877075261372</v>
       </c>
       <c r="K25">
-        <v>2.1470877075261372</v>
+        <v>5.84</v>
       </c>
       <c r="L25">
-        <v>2.1470877075261372</v>
+        <v>24</v>
       </c>
       <c r="M25">
-        <v>5.84</v>
+        <v>24</v>
       </c>
       <c r="N25">
-        <v>24</v>
-      </c>
-      <c r="O25">
-        <v>24</v>
-      </c>
-      <c r="P25">
         <v>16.5</v>
       </c>
     </row>
-    <row r="26" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A26">
         <v>297</v>
       </c>
@@ -5582,31 +5111,25 @@
         <v>1</v>
       </c>
       <c r="I26">
-        <v>5.9390243902439028</v>
+        <v>1.962802177102003</v>
       </c>
       <c r="J26">
-        <v>1.207299066858883</v>
+        <v>1.962802177102003</v>
       </c>
       <c r="K26">
-        <v>1.962802177102003</v>
+        <v>5.89</v>
       </c>
       <c r="L26">
-        <v>1.962802177102003</v>
+        <v>25</v>
       </c>
       <c r="M26">
-        <v>5.89</v>
+        <v>25</v>
       </c>
       <c r="N26">
-        <v>25</v>
-      </c>
-      <c r="O26">
-        <v>25</v>
-      </c>
-      <c r="P26">
         <v>9.5</v>
       </c>
     </row>
-    <row r="27" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A27">
         <v>156</v>
       </c>
@@ -5632,31 +5155,25 @@
         <v>1</v>
       </c>
       <c r="I27">
-        <v>0.33108494983277598</v>
+        <v>1.9442259245037321</v>
       </c>
       <c r="J27">
-        <v>12.299336263692661</v>
+        <v>1.9442259245037321</v>
       </c>
       <c r="K27">
-        <v>1.9442259245037321</v>
+        <v>5.33</v>
       </c>
       <c r="L27">
-        <v>1.9442259245037321</v>
+        <v>26</v>
       </c>
       <c r="M27">
-        <v>5.33</v>
+        <v>26</v>
       </c>
       <c r="N27">
-        <v>26</v>
-      </c>
-      <c r="O27">
-        <v>26</v>
-      </c>
-      <c r="P27">
         <v>21.5</v>
       </c>
     </row>
-    <row r="28" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A28">
         <v>112</v>
       </c>
@@ -5682,31 +5199,25 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>0.99935515361505822</v>
+        <v>1.8933596063359861</v>
       </c>
       <c r="J28">
-        <v>10.623687068343131</v>
+        <v>1.8933596063359861</v>
       </c>
       <c r="K28">
-        <v>1.8933596063359861</v>
+        <v>5.1100000000000003</v>
       </c>
       <c r="L28">
-        <v>1.8933596063359861</v>
+        <v>27</v>
       </c>
       <c r="M28">
-        <v>5.1100000000000003</v>
+        <v>27</v>
       </c>
       <c r="N28">
-        <v>27</v>
-      </c>
-      <c r="O28">
-        <v>27</v>
-      </c>
-      <c r="P28">
         <v>24</v>
       </c>
     </row>
-    <row r="29" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A29">
         <v>39</v>
       </c>
@@ -5732,31 +5243,25 @@
         <v>1</v>
       </c>
       <c r="I29">
-        <v>1.9261181640625</v>
+        <v>1.8879382948400121</v>
       </c>
       <c r="J29">
-        <v>8.7340189708084122</v>
+        <v>1.8879382948400121</v>
       </c>
       <c r="K29">
-        <v>1.8879382948400121</v>
+        <v>4.1900000000000004</v>
       </c>
       <c r="L29">
-        <v>1.8879382948400121</v>
+        <v>28</v>
       </c>
       <c r="M29">
-        <v>4.1900000000000004</v>
+        <v>28</v>
       </c>
       <c r="N29">
         <v>28</v>
       </c>
-      <c r="O29">
-        <v>28</v>
-      </c>
-      <c r="P29">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="30" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A30">
         <v>45</v>
       </c>
@@ -5782,31 +5287,25 @@
         <v>1</v>
       </c>
       <c r="I30">
-        <v>0.46783088235294118</v>
+        <v>1.875862643515253</v>
       </c>
       <c r="J30">
-        <v>11.57008919206247</v>
+        <v>1.875862643515253</v>
       </c>
       <c r="K30">
-        <v>1.875862643515253</v>
+        <v>0.96</v>
       </c>
       <c r="L30">
-        <v>1.875862643515253</v>
+        <v>29</v>
       </c>
       <c r="M30">
-        <v>0.96</v>
+        <v>29</v>
       </c>
       <c r="N30">
-        <v>29</v>
-      </c>
-      <c r="O30">
-        <v>29</v>
-      </c>
-      <c r="P30">
         <v>30</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A31">
         <v>203</v>
       </c>
@@ -5832,27 +5331,21 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>0.64117187499999995</v>
+        <v>1.8674013406850849</v>
       </c>
       <c r="J31">
-        <v>11.1669985212339</v>
+        <v>1.8674013406850849</v>
       </c>
       <c r="K31">
-        <v>1.8674013406850849</v>
+        <v>4.92</v>
       </c>
       <c r="L31">
-        <v>1.8674013406850849</v>
+        <v>30</v>
       </c>
       <c r="M31">
-        <v>4.92</v>
+        <v>30</v>
       </c>
       <c r="N31">
-        <v>30</v>
-      </c>
-      <c r="O31">
-        <v>30</v>
-      </c>
-      <c r="P31">
         <v>26</v>
       </c>
     </row>
